--- a/output/HS_Code_Summary_Sonik_Sports_TOUK_CZ0826.xlsx
+++ b/output/HS_Code_Summary_Sonik_Sports_TOUK_CZ0826.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1239,13 +1239,13 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>8903100000</t>
+          <t>8903110000</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Nafukovací čluny a kajaky pro zábavu nebo sport
-Zboží: 3 pol. – např. Nafukovací kajak SKEATER JAWZ 330; Nafukovací člun SONIK NOMAD 270; Nafukovací člun SONIK NOMAD 250</t>
+          <t>Nafukovací čluny (včetně nafukovacích člunů s pevným trupem), opatřené motorem nebo konstruované k tomu, aby jimi byly opatřeny, o čisté hmotnosti (bez motoru) nepřesahující 100 kg
+Zboží: 2 pol. – např. Nafukovací člun SONIK NOMAD 270; Nafukovací člun SONIK NOMAD 250</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1254,23 +1254,27 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>334.2</v>
+        <v>244.8</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>371.3</v>
+        <v>272</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>2674.62</v>
+        <v>1437</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr"/>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>OPRAVENO z 8903 10 00 (kód zrušen k 1. 1. 2022). Ověřte, zda jsou čluny konstruovány pro motor – viz „Poznámky a upozornění“.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1280,272 +1284,317 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t>8903120000</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Nafukovací čluny (včetně nafukovacích člunů s pevným trupem), nekonstruované k použití s motorem, o čisté hmotnosti nepřesahující 100 kg
+Zboží: 1 pol. – např. Nafukovací kajak SKEATER JAWZ 330</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>1237.62</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>DDP (místo chybí)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>OPRAVENO z 8903 10 00 (kód zrušen k 1. 1. 2022). Kajak není konstruován pro použití s motorem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Sonik Czech Logistics</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
           <t>9403202000</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Ostatní kovový nábytek – postele a lehátka
 Zboží: 1 pol. – např. Rybářské lehátko (spací systém) AXS COMFORT s paměťovou pěnou</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Čína (CN)</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n">
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F26" s="9" t="n">
         <v>228.6</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G26" s="9" t="n">
         <v>254</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H26" s="10" t="n">
         <v>1297.92</v>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Sonik Czech Logistics</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>9507100000</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Rybářské pruty
 Zboží: 24 pol. – např. Rybářský prut SONIK ANGL-R BARBEL 12', 1,75 lb (MULT); Rybářský prut NTR COMMERCIAL CARP FEEDER 10'; Rybářský prut NTR COMMERCIAL CARP FEEDER 9'</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Čína (CN)</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n">
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>3249</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>961.9</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G27" s="9" t="n">
         <v>1068.8</v>
       </c>
-      <c r="H26" s="10" t="n">
+      <c r="H27" s="10" t="n">
         <v>23492.46</v>
       </c>
-      <c r="I26" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>Pozor: rukojeti podběráků a latexové gumičky na návnadu patří spíše do 9507 90 – viz „Poznámky a upozornění“.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Sonik Czech Logistics</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>9507201000</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Udice (háčky) neopatřené nástavcem
 Zboží: 1 pol. – např. Trojháček POWER TREBLE ROUND JAW POINT vel. #2 (BL)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Čína (CN)</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F28" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G28" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="H27" s="10" t="n">
+      <c r="H28" s="10" t="n">
         <v>330</v>
       </c>
-      <c r="I27" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Sonik Czech Logistics</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>9507300000</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Rybářské navijáky
 Zboží: 9 pol. – např. Rybářský naviják IMPAX LONG CAST 5500; Bič / margin prut MARGIN MUNCHER 52 MARGIN 5,2 m; Bič / margin prut POWER EDGE CARP 80 MARGIN 8 m + nástavcová sada 2</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Čína (CN)</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>1695</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F29" s="9" t="n">
         <v>883.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G29" s="9" t="n">
         <v>981.4</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H29" s="10" t="n">
         <v>17186.28</v>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>Pozor: dvě položky (margin pruty, 400 ks) jsou zbožím čísla 9507 10 – viz „Poznámky a upozornění“.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="46" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Sonik Czech Logistics</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>9507900000</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Ostatní rybářské potřeby; podběráky, čeřeny a podobné sítě; návnady a podobné lovecké potřeby
 Zboží: 48 pol. – např. Vezírek (síť na uchování ryb) COMMERCIAL CARP 2,5 m, 3 ks; Skládací vážicí sak XTRACTOR; Trojnožka (stojan) na 3 pruty XTRACTOR</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Čína (CN)</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Čína (CN)</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>6831</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>1691.2</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G30" s="9" t="n">
         <v>1879.1</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H30" s="10" t="n">
         <v>14050.46</v>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>DDP (místo chybí)</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>CELKEM</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n">
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n">
         <v>14628</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F31" s="13" t="n">
         <v>5540.4</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G31" s="13" t="n">
         <v>6156</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H31" s="14" t="n">
         <v>77122.19</v>
       </c>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Hmotnosti jsou ROZPOČTENÉ z packing listu, nikoli vážené po položkách. PL uvádí hrubou a čistou hmotnost po paletách (26 palet, 6 156,0 / 5 540,4 kg);</t>
-        </is>
-      </c>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   hmotnost každé palety je rozpočtena na zboží na ní uložené v poměru fakturované hodnoty. Rozpad po položkách viz list „Položky faktury“ (sloupce M a N).</t>
+          <t>Hmotnosti jsou ROZPOČTENÉ z packing listu, nikoli vážené po položkách. PL uvádí hrubou a čistou hmotnost po paletách (26 palet, 6 156,0 / 5 540,4 kg);</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>POZOR: čistá hmotnost v PL je u všech 26 palet přesně 90 % hrubé, tj. paušální 10% odpočet obalu, nikoli zvážená hodnota — viz list „Poznámky a upozornění“.</t>
+          <t xml:space="preserve">   hmotnost každé palety je rozpočtena na zboží na ní uložené v poměru fakturované hodnoty. Rozpad po položkách viz list „Položky faktury“ (sloupce M a N).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Popis zboží: faktura je pouze v angličtině; české popisy jsou překladem fakturovaného označení, doplněným zněním celní nomenklatury k danému HS kódu.</t>
+          <t>POZOR: čistá hmotnost v PL je u všech 26 palet přesně 90 % hrubé, tj. paušální 10% odpočet obalu, nikoli zvážená hodnota — viz list „Poznámky a upozornění“.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Původní anglické znění je zachováno na listu „Položky faktury“ (sloupec O).</t>
+          <t>Popis zboží: faktura je pouze v angličtině; české popisy jsou překladem fakturovaného označení, doplněným zněním celní nomenklatury k danému HS kódu.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Původní anglické znění je zachováno na listu „Položky faktury“ (sloupec O).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Odesílatel: zásilka má jediného odesílatele (Sonik Czech Logistics), žádný HS kód proto není nutné dělit mezi více odesílatelů.</t>
         </is>
@@ -2455,7 +2504,7 @@
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>8903100000</t>
+          <t>8903110000</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -2470,7 +2519,7 @@
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Nafukovací čluny a kajaky pro zábavu nebo sport</t>
+          <t>Nafukovací čluny (včetně nafukovacích člunů s pevným trupem), opatřené motorem nebo konstruované k tomu, aby jimi byly opatřeny, o čisté hmotnosti (bez motoru) nepřesahující 100 kg</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
@@ -2516,7 +2565,7 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>8903100000</t>
+          <t>8903110000</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -2531,7 +2580,7 @@
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Nafukovací čluny a kajaky pro zábavu nebo sport</t>
+          <t>Nafukovací čluny (včetně nafukovacích člunů s pevným trupem), opatřené motorem nebo konstruované k tomu, aby jimi byly opatřeny, o čisté hmotnosti (bez motoru) nepřesahující 100 kg</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
@@ -7823,7 +7872,7 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>8903100000</t>
+          <t>8903120000</t>
         </is>
       </c>
       <c r="B103" s="17" t="inlineStr">
@@ -7838,7 +7887,7 @@
       </c>
       <c r="D103" s="18" t="inlineStr">
         <is>
-          <t>Nafukovací čluny a kajaky pro zábavu nebo sport</t>
+          <t>Nafukovací čluny (včetně nafukovacích člunů s pevným trupem), nekonstruované k použití s motorem, o čisté hmotnosti nepřesahující 100 kg</t>
         </is>
       </c>
       <c r="E103" s="17" t="inlineStr">
@@ -10485,7 +10534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10525,12 +10574,12 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>Čistá hmotnost je paušální, ne vážená</t>
+          <t>ODMÍTNUTÍ CELNÍM SYSTÉMEM — položka 8903 (nafukovací čluny) — OPRAVENO</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>Packing list nově uvádí čistou hmotnost — u VŠECH 26 palet je ale přesně 90,0 % hrubé hmotnosti (6 156,0 → 5 540,4 kg). Jde tedy o plošný 10% odpočet obalu, nikoli o zvážené hodnoty. Pro celní prohlášení je to použitelné, ale pokud by celní úřad čistou hmotnost zpochybnil, není čím ji doložit. Doporučuji si u skladu ověřit, zda je 10 % podložený odhad obalu, a mít odpověď připravenou.</t>
+          <t>Celní systém odmítl položku 10 deklarace: „Prohlášení o podpoložce podléhající právním omezením (čistá hmotnost / doplňková jednotka)“, kolonky 33, 38, 41 // datové prvky 6/14, 6/15, 6/1, 6/2. PŘÍČINOU NENÍ ČISTÁ HMOTNOST, ale sazební zařazení. Faktura uvádí 8903 10 00 — tento kód byl ZRUŠEN k 1. 1. 2022, kdy se podpoložka rozdělila podle hmotnosti a motorizace. Deklarace proto použila zbytkovou podpoložku 8903 19 00, která je určena pro plavidla o čisté hmotnosti NAD 100 kg za kus. Deklarováno bylo 8 ks / 334,2 kg = 41,8 kg na kus, tedy pod 100 kg — systém proto hlásí rozpor mezi podpoložkou a poměrem čistá hmotnost / doplňková jednotka. Snížení ani zvýšení čisté hmotnosti chybu neodstraní; opravit je nutné KÓD. V tomto souhrnu je zboží nově zařazeno do 8903 11 00 (čluny Nomad, 6 ks) a 8903 12 00 (kajak, 2 ks) — obojí do 100 kg/ks.</t>
         </is>
       </c>
     </row>
@@ -10542,12 +10591,12 @@
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>Dodací podmínka — chybí místo určení</t>
+          <t>8903 11 00 vs. 8903 12 00 — ověřte motorizaci</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>Faktura uvádí pouze „INCOTERMS: DDP“ bez města / místa určení. DDP je bez uvedení místa neúplná. Doplňte místo dodání (nejpravděpodobněji „DDP Blyth, Spojené království“) a nechte fakturu opravit před podáním celního prohlášení. Toto je po doplnění PL jediný chybějící údaj na faktuře.</t>
+          <t>Rozdíl mezi oběma podpoložkami je jediný: zda je člun opatřen motorem nebo konstruován k tomu, aby jím byl opatřen (8903 11 00), nebo nikoli (8903 12 00). SONIK NOMAD 250 a 270 jsem zařadila do 8903 11 00 s předpokladem, že mají zrcadlo (transom) pro závěsný motor. POKUD pro motor konstruovány NEJSOU, patří i ony do 8903 12 00 — dejte vědět a přepíšu. SKEATER JAWZ 330 je nafukovací kajak, pro motor konstruovaný není, proto 8903 12 00.</t>
         </is>
       </c>
     </row>
@@ -10559,97 +10608,97 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
+          <t>Zkontrolujte stáří číselníku HS na faktuře</t>
+        </is>
+      </c>
+      <c r="C6" s="37" t="inlineStr">
+        <is>
+          <t>Kód 8903 10 00 je na faktuře uveden více než tři roky po svém zrušení. Číselník zboží u dodavatele tedy nemusí být aktualizovaný podle novějších znění kombinované nomenklatury. Doporučuji nechat ověřit i ostatní kódy na faktuře proti aktuální KN, než se stejný problém objeví u jiné položky.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>K ŘEŠENÍ</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>Čistá hmotnost je paušální, ne vážená</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Packing list nově uvádí čistou hmotnost — u VŠECH 26 palet je ale přesně 90,0 % hrubé hmotnosti (6 156,0 → 5 540,4 kg). Jde tedy o plošný 10% odpočet obalu, nikoli o zvážené hodnoty. Pro celní prohlášení je to použitelné, ale pokud by celní úřad čistou hmotnost zpochybnil, není čím ji doložit. Doporučuji si u skladu ověřit, zda je 10 % podložený odhad obalu, a mít odpověď připravenou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>K ŘEŠENÍ</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Dodací podmínka — chybí místo určení</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Faktura uvádí pouze „INCOTERMS: DDP“ bez města / místa určení. DDP je bez uvedení místa neúplná. Doplňte místo dodání (nejpravděpodobněji „DDP Blyth, Spojené království“) a nechte fakturu opravit před podáním celního prohlášení. Toto je po doplnění PL jediný chybějící údaj na faktuře.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>UPOZORNĚNÍ</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
           <t>Preferenční věta — NENÍ NA FAKTUŘE</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Obchodní faktura NEOBSAHUJE prohlášení o preferenčním původu. Zboží je původem z Číny a z Maďarska: zboží čínského původu (naprostá většina zásilky) preferenci získat nemůže. Zboží maďarského původu (HS 5404190090, 256 ks / 815,20 GBP) je zbožím s původem v EU a PŘI DOVOZU do Spojeného království by na základě dohody EU–UK (TCA) mělo nárok na nulové clo, pokud by na faktuře bylo uvedeno prohlášení o původu. Bez něj zaplatí britský dovozce plnou sazbu pro třetí země. Doporučuji doplnit prohlášení o původu podle dohody EU–UK pouze pro položky maďarského původu.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>UPOZORNĚNÍ</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Země původu — smíšená</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>Čína (15 HS kódů, 14 372 ks, 76 306,99 GBP) a Maďarsko (HS 5404190090, 256 ks, 815,20 GBP). Původ je nutné deklarovat po položkách — nedeklarujte jednu zemi původu pro celou zásilku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Čína (16 HS kódů, 14 372 ks, 76 306,99 GBP) a Maďarsko (HS 5404190090, 256 ks, 815,20 GBP). Původ je nutné deklarovat po položkách — nedeklarujte jednu zemi původu pro celou zásilku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>UPOZORNĚNÍ</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Sazební zařazení — dvě položky ke kontrole</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>a) HS 9507300000 (rybářské navijáky) zahrnuje podle faktury i „POWER EDGE CARP 80 MARGIN 8M“ (100 ks) a „MARGIN MUNCHER 52 MARGIN 5,2M“ (300 ks) — jde o biče / margin pruty, tedy zboží čísla 9507 10. b) HS 9507100000 (rybářské pruty) zahrnuje i rukojeti podběráků (20500007, 20500008) a latexové gumičky na návnadu (22100300, 22100303, 22100304) — ty patří spíše do 9507 90. Zařazení je ponecháno tak, jak je uvedeno na faktuře; potvrďte prosím, zda je opravit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>Packing list — kompletní, souhlasí s revidovanou CI</t>
-        </is>
-      </c>
-      <c r="C9" s="41" t="inlineStr">
-        <is>
-          <t>Nový PL (WH2_to_WH1_PL.xlsx) pokrývá 26 palet a obsahuje všech 120 řádků revidované faktury ve stejném pořadí, se shodnými kódy zboží i množstvími (sloupec Variance je u všech řádků nulový). Oproti původnímu plánu z 13. 8. přibylo 5 palet (Paleta 22–26, +940,0 kg GW) pro dodatečně přidané cargo. Číslování palet je nově souvislé 1–26; v původním plánu chybělo označení u jedné palety.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="inlineStr">
-        <is>
-          <t>Nová HS položka 4016999190</t>
-        </is>
-      </c>
-      <c r="C10" s="41" t="inlineStr">
-        <is>
-          <t>Revidovaná CI zavedla nový HS kód 4016999190 (ostatní výrobky z vulkanizovaného kaučuku) — HC0046 STANZ RUBBER ROD GRIP MEDIUM, 100 ks / 57,00 GBP, původ Čína, uloženo na Paletě 26. Zásilka má tedy 16 HS kódů.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="66" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="B11" s="40" t="inlineStr">
-        <is>
-          <t>CBAM — na tento pohyb se nevztahuje</t>
-        </is>
-      </c>
-      <c r="C11" s="41" t="inlineStr">
-        <is>
-          <t>CBAM se uplatňuje na zboží DOVÁŽENÉ do EU. Zde jde o VÝVOZ z EU (ČR) do Spojeného království, povinnost CBAM tedy nevzniká a není koho v registru dohledávat (příjemce není český). Pro informaci: HS 7616999099 (ostatní výrobky z hliníku, 430 ks / 1 458,20 GBP) JE položkou v režimu CBAM a při opačném pohybu (UK → ČR) by hlášení CBAM vyvolala. HS 7323930090 (výrobky pro domácnost z nerezavějící oceli) do režimu CBAM nespadá.</t>
         </is>
       </c>
     </row>
@@ -10661,12 +10710,12 @@
       </c>
       <c r="B12" s="40" t="inlineStr">
         <is>
-          <t>Registr CBAM — kupující je veden na sdíleném účtu</t>
+          <t>Packing list — kompletní, souhlasí s revidovanou CI</t>
         </is>
       </c>
       <c r="C12" s="41" t="inlineStr">
         <is>
-          <t>reference/CBAM_receivers_CZ.xlsx, list List1, řádek 7: „Sonik Sports Limited“ (EORI CZ00015236976) je uveden mezi společnostmi mimo EU, které používají náš sdílený účet CBAM-CZ-2025-QGM67089385721. Relevantní pouze při pohybu zboží DO EU; zde se neuplatní. Pozor: registr eviduje u britské společnosti české EORI CZ00015236976, zatímco faktura uvádí toto EORI u Sonik Czech Logistics a britské společnosti přiřazuje GB923608624000 — doporučuji v registru sjednotit.</t>
+          <t>Nový PL (WH2_to_WH1_PL.xlsx) pokrývá 26 palet a obsahuje všech 120 řádků revidované faktury ve stejném pořadí, se shodnými kódy zboží i množstvími (sloupec Variance je u všech řádků nulový). Oproti původnímu plánu z 13. 8. přibylo 5 palet (Paleta 22–26, +940,0 kg GW) pro dodatečně přidané cargo. Číslování palet je nově souvislé 1–26; v původním plánu chybělo označení u jedné palety.</t>
         </is>
       </c>
     </row>
@@ -10678,12 +10727,12 @@
       </c>
       <c r="B13" s="40" t="inlineStr">
         <is>
-          <t>Antidumping — nezjištěn</t>
+          <t>Nová HS položka 4016999190</t>
         </is>
       </c>
       <c r="C13" s="41" t="inlineStr">
         <is>
-          <t>Pro uvedené HS kódy nebylo u tohoto vývozu identifikováno žádné antidumpingové opatření EU; antidumpingová cla EU se na vývoz neuplatňují. Na britské dovozní straně ověřte obchodní ochranná opatření UK u hliníkových výrobků čínského původu (HS 7616999099).</t>
+          <t>Revidovaná CI zavedla nový HS kód 4016999190 (ostatní výrobky z vulkanizovaného kaučuku) — HC0046 STANZ RUBBER ROD GRIP MEDIUM, 100 ks / 57,00 GBP, původ Čína, uloženo na Paletě 26. Zásilka má tedy 16 HS kódů.</t>
         </is>
       </c>
     </row>
@@ -10695,12 +10744,12 @@
       </c>
       <c r="B14" s="40" t="inlineStr">
         <is>
-          <t>Obchodní sleva</t>
+          <t>CBAM — na tento pohyb se nevztahuje</t>
         </is>
       </c>
       <c r="C14" s="41" t="inlineStr">
         <is>
-          <t>Na faktuře není uvedena žádná sleva. Celní hodnoty v tomto souhrnu odpovídají fakturovaným hodnotám položek; žádná poměrná sleva nebyla rozpočítána.</t>
+          <t>CBAM se uplatňuje na zboží DOVÁŽENÉ do EU. Zde jde o VÝVOZ z EU (ČR) do Spojeného království, povinnost CBAM tedy nevzniká a není koho v registru dohledávat (příjemce není český). Pro informaci: HS 7616999099 (ostatní výrobky z hliníku, 430 ks / 1 458,20 GBP) JE položkou v režimu CBAM a při opačném pohybu (UK → ČR) by hlášení CBAM vyvolala. HS 7323930090 (výrobky pro domácnost z nerezavějící oceli) do režimu CBAM nespadá.</t>
         </is>
       </c>
     </row>
@@ -10712,12 +10761,12 @@
       </c>
       <c r="B15" s="40" t="inlineStr">
         <is>
-          <t>Duplicitní kódy zboží na revidované CI</t>
+          <t>Registr CBAM — kupující je veden na sdíleném účtu</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
         <is>
-          <t>Čtyři kódy jsou na faktuře i v PL uvedeny dvakrát — RC0021, 20200003, 20200004 a 20100053 — jednou v původním rozsahu a podruhé v bloku dodatečně přidaného carga. Jednotkové ceny jsou shodné, jde tedy o dodatečné množství téhož zboží. Řádky faktury a PL jsou párovány podle pořadí (kód i množství souhlasí u všech 120 řádků), takže se obě části nepomíchaly.</t>
+          <t>reference/CBAM_receivers_CZ.xlsx, list List1, řádek 7: „Sonik Sports Limited“ (EORI CZ00015236976) je uveden mezi společnostmi mimo EU, které používají náš sdílený účet CBAM-CZ-2025-QGM67089385721. Relevantní pouze při pohybu zboží DO EU; zde se neuplatní. Pozor: registr eviduje u britské společnosti české EORI CZ00015236976, zatímco faktura uvádí toto EORI u Sonik Czech Logistics a britské společnosti přiřazuje GB923608624000 — doporučuji v registru sjednotit.</t>
         </is>
       </c>
     </row>
@@ -10729,12 +10778,12 @@
       </c>
       <c r="B16" s="40" t="inlineStr">
         <is>
-          <t>Popis zboží — jazyk</t>
+          <t>Antidumping — nezjištěn</t>
         </is>
       </c>
       <c r="C16" s="41" t="inlineStr">
         <is>
-          <t>Zdrojové doklady neobsahují žádný český text. České popisy jsou překladem anglického označení z faktury; obchodní značky, názvy modelů a rozměry jsou ponechány v původním znění. Původní anglický popis je uveden na listu „Položky faktury“ (sloupec O). U několika zkratek na faktuře byl význam odvozen (P/O, MULT, BL, 3PCS) — v případě pochybností ověřte u dodavatele.</t>
+          <t>Pro uvedené HS kódy nebylo u tohoto vývozu identifikováno žádné antidumpingové opatření EU; antidumpingová cla EU se na vývoz neuplatňují. Na britské dovozní straně ověřte obchodní ochranná opatření UK u hliníkových výrobků čínského původu (HS 7616999099).</t>
         </is>
       </c>
     </row>
@@ -10746,27 +10795,78 @@
       </c>
       <c r="B17" s="40" t="inlineStr">
         <is>
-          <t>Způsob klasifikace</t>
+          <t>Obchodní sleva</t>
         </is>
       </c>
       <c r="C17" s="41" t="inlineStr">
         <is>
-          <t>Klasifikováno nejprve podle odesílatele, poté podle HS kódu. Zásilka má jediného odesílatele (Sonik Czech Logistics), všech 16 jedinečných HS kódů se proto vyskytuje jednou.</t>
+          <t>Na faktuře není uvedena žádná sleva. Celní hodnoty v tomto souhrnu odpovídají fakturovaným hodnotám položek; žádná poměrná sleva nebyla rozpočítána.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="66" customHeight="1">
       <c r="A18" s="39" t="inlineStr">
         <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>Duplicitní kódy zboží na revidované CI</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Čtyři kódy jsou na faktuře i v PL uvedeny dvakrát — RC0021, 20200003, 20200004 a 20100053 — jednou v původním rozsahu a podruhé v bloku dodatečně přidaného carga. Jednotkové ceny jsou shodné, jde tedy o dodatečné množství téhož zboží. Řádky faktury a PL jsou párovány podle pořadí (kód i množství souhlasí u všech 120 řádků), takže se obě části nepomíchaly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>Popis zboží — jazyk</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Zdrojové doklady neobsahují žádný český text. České popisy jsou překladem anglického označení z faktury; obchodní značky, názvy modelů a rozměry jsou ponechány v původním znění. Původní anglický popis je uveden na listu „Položky faktury“ (sloupec O). U několika zkratek na faktuře byl význam odvozen (P/O, MULT, BL, 3PCS) — v případě pochybností ověřte u dodavatele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>Způsob klasifikace</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Klasifikováno nejprve podle odesílatele, poté podle HS kódu. Zásilka má jediného odesílatele (Sonik Czech Logistics), všech 17 jedinečných HS kódů se proto vyskytuje jednou (16 z faktury, přičemž 8903 10 00 bylo rozděleno na 8903 11 00 a 8903 12 00).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
           <t>KONTROLA</t>
         </is>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>Odsouhlasení</t>
         </is>
       </c>
-      <c r="C18" s="41" t="inlineStr">
+      <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Faktura 14 628 ks / 77 122,19 GBP = součet souhrnu (souhlasí s řádkem TOTAL na faktuře). Packing list 14 628 ks na 26 paletách = součet faktury, u všech 120 řádků nulová variance. Hmotnosti palet 6 156,0 kg GW / 5 540,4 kg NW = součty alokovaných hmotností v souhrnu.</t>
         </is>
